--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y335"/>
+  <dimension ref="A1:Y338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27104,7 +27104,7 @@
         <v>322.59</v>
       </c>
       <c r="L333" t="n">
-        <v>332.5</v>
+        <v>341.3</v>
       </c>
       <c r="M333" t="inlineStr"/>
       <c r="N333" t="n">
@@ -27183,7 +27183,7 @@
         <v>320.48</v>
       </c>
       <c r="L334" t="n">
-        <v>334.22</v>
+        <v>346.52</v>
       </c>
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="n">
@@ -27256,13 +27256,13 @@
         <v>328.59</v>
       </c>
       <c r="J335" t="n">
-        <v>329.49</v>
+        <v>343.01</v>
       </c>
       <c r="K335" t="n">
         <v>314.4</v>
       </c>
       <c r="L335" t="n">
-        <v>334.22</v>
+        <v>346.52</v>
       </c>
       <c r="M335" t="n">
         <v>251.91</v>
@@ -27274,7 +27274,7 @@
         <v>321.97</v>
       </c>
       <c r="P335" t="n">
-        <v>339.19</v>
+        <v>348.41</v>
       </c>
       <c r="Q335" t="n">
         <v>331.01</v>
@@ -27301,6 +27301,249 @@
         <v>345.88</v>
       </c>
       <c r="Y335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>345.67</v>
+      </c>
+      <c r="C336" t="n">
+        <v>336.14</v>
+      </c>
+      <c r="D336" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="E336" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="F336" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="G336" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="H336" t="n">
+        <v>318.57</v>
+      </c>
+      <c r="I336" t="n">
+        <v>325.17</v>
+      </c>
+      <c r="J336" t="n">
+        <v>348</v>
+      </c>
+      <c r="K336" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="L336" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="M336" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="N336" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="O336" t="n">
+        <v>310</v>
+      </c>
+      <c r="P336" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="R336" t="n">
+        <v>320.96</v>
+      </c>
+      <c r="S336" t="n">
+        <v>354.47</v>
+      </c>
+      <c r="T336" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="U336" t="n">
+        <v>333.81</v>
+      </c>
+      <c r="V336" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="W336" t="n">
+        <v>342.07</v>
+      </c>
+      <c r="X336" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>345.67</v>
+      </c>
+      <c r="C337" t="n">
+        <v>336.14</v>
+      </c>
+      <c r="D337" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="E337" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="F337" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="G337" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="H337" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="I337" t="n">
+        <v>325.17</v>
+      </c>
+      <c r="J337" t="n">
+        <v>348</v>
+      </c>
+      <c r="K337" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="L337" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="M337" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="N337" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="O337" t="n">
+        <v>300.91</v>
+      </c>
+      <c r="P337" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="R337" t="n">
+        <v>320.96</v>
+      </c>
+      <c r="S337" t="n">
+        <v>352.19</v>
+      </c>
+      <c r="T337" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="U337" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="V337" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="W337" t="n">
+        <v>338.76</v>
+      </c>
+      <c r="X337" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>343.08</v>
+      </c>
+      <c r="C338" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="D338" t="n">
+        <v>324.77</v>
+      </c>
+      <c r="E338" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="F338" t="n">
+        <v>310.83</v>
+      </c>
+      <c r="G338" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="H338" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="I338" t="n">
+        <v>309.57</v>
+      </c>
+      <c r="J338" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="K338" t="n">
+        <v>302.42</v>
+      </c>
+      <c r="L338" t="n">
+        <v>323.29</v>
+      </c>
+      <c r="M338" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="N338" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="O338" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="P338" t="n">
+        <v>328.08</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>312.36</v>
+      </c>
+      <c r="R338" t="n">
+        <v>322.57</v>
+      </c>
+      <c r="S338" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="T338" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="U338" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="V338" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="W338" t="n">
+        <v>338.76</v>
+      </c>
+      <c r="X338" t="n">
+        <v>345.62</v>
+      </c>
+      <c r="Y338" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27317,7 +27560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30940,6 +31183,36 @@
       </c>
       <c r="B362" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>
@@ -31108,28 +31381,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7664993013752189</v>
+        <v>0.7473972774902912</v>
       </c>
       <c r="J2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1242444263499005</v>
+        <v>0.1200591053834797</v>
       </c>
       <c r="M2" t="n">
-        <v>11.97175527707283</v>
+        <v>11.95707642141918</v>
       </c>
       <c r="N2" t="n">
-        <v>227.5727457209224</v>
+        <v>226.705054718708</v>
       </c>
       <c r="O2" t="n">
-        <v>15.08551443341997</v>
+        <v>15.05672788884451</v>
       </c>
       <c r="P2" t="n">
-        <v>336.0314268476574</v>
+        <v>336.2421013050798</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31186,28 +31459,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1610029177361296</v>
+        <v>-0.1593765104396153</v>
       </c>
       <c r="J3" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004948310938911238</v>
+        <v>0.004930717138065144</v>
       </c>
       <c r="M3" t="n">
-        <v>12.00466474403561</v>
+        <v>11.91253220033434</v>
       </c>
       <c r="N3" t="n">
-        <v>289.2114281960726</v>
+        <v>286.6653134122733</v>
       </c>
       <c r="O3" t="n">
-        <v>17.0062173394342</v>
+        <v>16.93119350229845</v>
       </c>
       <c r="P3" t="n">
-        <v>338.1747180977107</v>
+        <v>338.1570262460433</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31264,28 +31537,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1244923584464986</v>
+        <v>-0.1424150463602835</v>
       </c>
       <c r="J4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002590846231105837</v>
+        <v>0.003433609603211929</v>
       </c>
       <c r="M4" t="n">
-        <v>13.24332977459044</v>
+        <v>13.24842243440673</v>
       </c>
       <c r="N4" t="n">
-        <v>329.0052164844544</v>
+        <v>327.1448336824633</v>
       </c>
       <c r="O4" t="n">
-        <v>18.13850094369583</v>
+        <v>18.08714553716156</v>
       </c>
       <c r="P4" t="n">
-        <v>335.6134875802475</v>
+        <v>335.8099368416441</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31342,28 +31615,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7859261596124595</v>
+        <v>0.6718967081893222</v>
       </c>
       <c r="J5" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06116861698430265</v>
+        <v>0.0429837721503199</v>
       </c>
       <c r="M5" t="n">
-        <v>18.55357239790424</v>
+        <v>19.04931613534733</v>
       </c>
       <c r="N5" t="n">
-        <v>524.8732744587362</v>
+        <v>560.9259707192462</v>
       </c>
       <c r="O5" t="n">
-        <v>22.91011292985559</v>
+        <v>23.68387575375378</v>
       </c>
       <c r="P5" t="n">
-        <v>324.6551555365443</v>
+        <v>325.9060026676552</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31420,28 +31693,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3394853299834406</v>
+        <v>0.331390695042441</v>
       </c>
       <c r="J6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008851259737415074</v>
+        <v>0.008576852807590019</v>
       </c>
       <c r="M6" t="n">
-        <v>19.2779720196944</v>
+        <v>19.16390877345485</v>
       </c>
       <c r="N6" t="n">
-        <v>713.3334378477365</v>
+        <v>707.1377160987984</v>
       </c>
       <c r="O6" t="n">
-        <v>26.70830278860371</v>
+        <v>26.59206114799675</v>
       </c>
       <c r="P6" t="n">
-        <v>308.6203790179794</v>
+        <v>308.7090186116847</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31498,28 +31771,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07198699339573485</v>
+        <v>0.06199791907083704</v>
       </c>
       <c r="J7" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006356840411497755</v>
+        <v>0.0004792342775269409</v>
       </c>
       <c r="M7" t="n">
-        <v>15.50940969904041</v>
+        <v>15.44827038989944</v>
       </c>
       <c r="N7" t="n">
-        <v>450.3105584258403</v>
+        <v>446.6562836255103</v>
       </c>
       <c r="O7" t="n">
-        <v>21.22052210540166</v>
+        <v>21.13424433533194</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0365433418775</v>
+        <v>323.1457595832088</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31576,28 +31849,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1250755080121428</v>
+        <v>0.08952574150058318</v>
       </c>
       <c r="J8" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007286978804569078</v>
+        <v>0.003672542402481049</v>
       </c>
       <c r="M8" t="n">
-        <v>8.799006942794763</v>
+        <v>8.944072998840825</v>
       </c>
       <c r="N8" t="n">
-        <v>118.4670352242372</v>
+        <v>121.8172539392017</v>
       </c>
       <c r="O8" t="n">
-        <v>10.88425630092554</v>
+        <v>11.03708539149724</v>
       </c>
       <c r="P8" t="n">
-        <v>329.7582466716907</v>
+        <v>330.1454116794267</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31654,28 +31927,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07905805882345103</v>
+        <v>0.05510431762074602</v>
       </c>
       <c r="J9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K9" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001186519578320833</v>
+        <v>0.0005817682783368916</v>
       </c>
       <c r="M9" t="n">
-        <v>12.34109530195484</v>
+        <v>12.39755159596115</v>
       </c>
       <c r="N9" t="n">
-        <v>293.327529595827</v>
+        <v>293.0740460936482</v>
       </c>
       <c r="O9" t="n">
-        <v>17.12680733808339</v>
+        <v>17.11940554147977</v>
       </c>
       <c r="P9" t="n">
-        <v>332.587779612029</v>
+        <v>332.8486581372898</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31732,28 +32005,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08779385452310033</v>
+        <v>0.1261708167904721</v>
       </c>
       <c r="J10" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K10" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001869101754550351</v>
+        <v>0.00383051170348514</v>
       </c>
       <c r="M10" t="n">
-        <v>12.76629527782052</v>
+        <v>12.82243644793013</v>
       </c>
       <c r="N10" t="n">
-        <v>227.0774417802258</v>
+        <v>230.1753284285758</v>
       </c>
       <c r="O10" t="n">
-        <v>15.06908894990755</v>
+        <v>15.17153019403698</v>
       </c>
       <c r="P10" t="n">
-        <v>319.7326222661636</v>
+        <v>319.3122680019385</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31810,28 +32083,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07550946557715268</v>
+        <v>0.05460771129485705</v>
       </c>
       <c r="J11" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K11" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001151581103416066</v>
+        <v>0.0006095749731656053</v>
       </c>
       <c r="M11" t="n">
-        <v>13.63994172520059</v>
+        <v>13.6414192305115</v>
       </c>
       <c r="N11" t="n">
-        <v>274.0960734520812</v>
+        <v>273.0731183988015</v>
       </c>
       <c r="O11" t="n">
-        <v>16.55584710765599</v>
+        <v>16.52492415712706</v>
       </c>
       <c r="P11" t="n">
-        <v>314.441223847346</v>
+        <v>314.6696801125975</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31888,28 +32161,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3639212322432525</v>
+        <v>0.4010018831178611</v>
       </c>
       <c r="J12" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K12" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03305417089654838</v>
+        <v>0.03970880575624136</v>
       </c>
       <c r="M12" t="n">
-        <v>12.08635490826886</v>
+        <v>12.14717410899306</v>
       </c>
       <c r="N12" t="n">
-        <v>216.1794923479462</v>
+        <v>218.7427302191126</v>
       </c>
       <c r="O12" t="n">
-        <v>14.70304364231931</v>
+        <v>14.78995369225721</v>
       </c>
       <c r="P12" t="n">
-        <v>318.6332397105612</v>
+        <v>318.2319532068291</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31966,28 +32239,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6744441190551381</v>
+        <v>-0.764608308000791</v>
       </c>
       <c r="J13" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K13" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02270365116643325</v>
+        <v>0.02890045613715786</v>
       </c>
       <c r="M13" t="n">
-        <v>28.09034782566955</v>
+        <v>28.39649223896004</v>
       </c>
       <c r="N13" t="n">
-        <v>1102.102927524257</v>
+        <v>1115.558927942701</v>
       </c>
       <c r="O13" t="n">
-        <v>33.19793559130232</v>
+        <v>33.39998395123419</v>
       </c>
       <c r="P13" t="n">
-        <v>320.2019745879601</v>
+        <v>321.1716604191314</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32044,28 +32317,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2252461939484767</v>
+        <v>-0.2192048640495821</v>
       </c>
       <c r="J14" t="n">
+        <v>337</v>
+      </c>
+      <c r="K14" t="n">
         <v>334</v>
       </c>
-      <c r="K14" t="n">
-        <v>331</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.00604436951903875</v>
+        <v>0.005818250542006465</v>
       </c>
       <c r="M14" t="n">
-        <v>18.54794121548596</v>
+        <v>18.41416133365595</v>
       </c>
       <c r="N14" t="n">
-        <v>465.4745768114342</v>
+        <v>461.6623756858295</v>
       </c>
       <c r="O14" t="n">
-        <v>21.57485983294988</v>
+        <v>21.48632997246923</v>
       </c>
       <c r="P14" t="n">
-        <v>304.6685882155176</v>
+        <v>304.60299976056</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32122,28 +32395,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1498475463265431</v>
+        <v>0.1420178510285227</v>
       </c>
       <c r="J15" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K15" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003495300995398298</v>
+        <v>0.003189799044963082</v>
       </c>
       <c r="M15" t="n">
-        <v>16.19642563162193</v>
+        <v>16.1088120001134</v>
       </c>
       <c r="N15" t="n">
-        <v>357.6945795905516</v>
+        <v>354.9063910760921</v>
       </c>
       <c r="O15" t="n">
-        <v>18.91281522118142</v>
+        <v>18.83895939472486</v>
       </c>
       <c r="P15" t="n">
-        <v>303.8456929515546</v>
+        <v>303.9308656455211</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32200,28 +32473,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3028965055093912</v>
+        <v>0.3392858421136531</v>
       </c>
       <c r="J16" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K16" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008429213391055734</v>
+        <v>0.01063795450599869</v>
       </c>
       <c r="M16" t="n">
-        <v>20.0345157880061</v>
+        <v>20.03230106054498</v>
       </c>
       <c r="N16" t="n">
-        <v>594.375486438125</v>
+        <v>594.1794272242802</v>
       </c>
       <c r="O16" t="n">
-        <v>24.37981719451819</v>
+        <v>24.37579593006719</v>
       </c>
       <c r="P16" t="n">
-        <v>314.1374676560518</v>
+        <v>313.7378496375323</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32278,28 +32551,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6865144077071917</v>
+        <v>-0.6806978549314379</v>
       </c>
       <c r="J17" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K17" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03793483042840573</v>
+        <v>0.03795346871191974</v>
       </c>
       <c r="M17" t="n">
-        <v>21.40338114081258</v>
+        <v>21.23392697074636</v>
       </c>
       <c r="N17" t="n">
-        <v>658.1668943415395</v>
+        <v>651.997601484853</v>
       </c>
       <c r="O17" t="n">
-        <v>25.65476357991902</v>
+        <v>25.53424370301288</v>
       </c>
       <c r="P17" t="n">
-        <v>329.9187797757445</v>
+        <v>329.8548406345076</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32356,28 +32629,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1045781030785901</v>
+        <v>-0.1084066254904051</v>
       </c>
       <c r="J18" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K18" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005142548158134419</v>
+        <v>0.005614922228217689</v>
       </c>
       <c r="M18" t="n">
-        <v>8.463250235909902</v>
+        <v>8.414329548575418</v>
       </c>
       <c r="N18" t="n">
-        <v>116.3897922698456</v>
+        <v>115.4004061582148</v>
       </c>
       <c r="O18" t="n">
-        <v>10.7884100899922</v>
+        <v>10.74245810595577</v>
       </c>
       <c r="P18" t="n">
-        <v>326.6096351712214</v>
+        <v>326.6515825948189</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32434,28 +32707,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2229007802455811</v>
+        <v>0.2256609059137669</v>
       </c>
       <c r="J19" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K19" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03751181272043824</v>
+        <v>0.03902036322193769</v>
       </c>
       <c r="M19" t="n">
-        <v>6.345909482910637</v>
+        <v>6.300828630766577</v>
       </c>
       <c r="N19" t="n">
-        <v>70.73100543495329</v>
+        <v>70.13241915607107</v>
       </c>
       <c r="O19" t="n">
-        <v>8.410172735143631</v>
+        <v>8.374510084540532</v>
       </c>
       <c r="P19" t="n">
-        <v>345.7739626083797</v>
+        <v>345.7439041213494</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32512,28 +32785,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07976296569659594</v>
+        <v>0.09428253784568381</v>
       </c>
       <c r="J20" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K20" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004307709718459618</v>
+        <v>0.006055877555797839</v>
       </c>
       <c r="M20" t="n">
-        <v>7.096725672757343</v>
+        <v>7.123902033130928</v>
       </c>
       <c r="N20" t="n">
-        <v>81.74440886571195</v>
+        <v>81.73820268591555</v>
       </c>
       <c r="O20" t="n">
-        <v>9.041261464293129</v>
+        <v>9.040918243514623</v>
       </c>
       <c r="P20" t="n">
-        <v>344.4511685154661</v>
+        <v>344.2930925465403</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32590,28 +32863,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2898035525403303</v>
+        <v>0.2906442665746281</v>
       </c>
       <c r="J21" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K21" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02106023354002817</v>
+        <v>0.02152440481241513</v>
       </c>
       <c r="M21" t="n">
-        <v>11.89486824822854</v>
+        <v>11.81102382334768</v>
       </c>
       <c r="N21" t="n">
-        <v>215.2394125970729</v>
+        <v>213.379145209852</v>
       </c>
       <c r="O21" t="n">
-        <v>14.67103992895776</v>
+        <v>14.60750304500574</v>
       </c>
       <c r="P21" t="n">
-        <v>321.4749106311808</v>
+        <v>321.4657335354685</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32668,28 +32941,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3888804682776781</v>
+        <v>0.4272414007126071</v>
       </c>
       <c r="J22" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K22" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02336163996345897</v>
+        <v>0.02813397901038939</v>
       </c>
       <c r="M22" t="n">
-        <v>15.05795526960886</v>
+        <v>15.14082006239156</v>
       </c>
       <c r="N22" t="n">
-        <v>352.0826953563559</v>
+        <v>353.9213924724298</v>
       </c>
       <c r="O22" t="n">
-        <v>18.76386674852377</v>
+        <v>18.81279863477069</v>
       </c>
       <c r="P22" t="n">
-        <v>302.0363803199345</v>
+        <v>301.6193104263991</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32746,28 +33019,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4951134074803258</v>
+        <v>0.5010564544065578</v>
       </c>
       <c r="J23" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K23" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1200943463269799</v>
+        <v>0.1243114794108495</v>
       </c>
       <c r="M23" t="n">
-        <v>7.764207953606012</v>
+        <v>7.717503263007018</v>
       </c>
       <c r="N23" t="n">
-        <v>99.651127577488</v>
+        <v>98.8997130027869</v>
       </c>
       <c r="O23" t="n">
-        <v>9.982541138281775</v>
+        <v>9.944833482908948</v>
       </c>
       <c r="P23" t="n">
-        <v>323.0543458909248</v>
+        <v>322.9896326722451</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32824,28 +33097,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1583451340181976</v>
+        <v>0.1597090213591316</v>
       </c>
       <c r="J24" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K24" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L24" t="n">
-        <v>0.04355860814276813</v>
+        <v>0.04498002109679922</v>
       </c>
       <c r="M24" t="n">
-        <v>3.906814235700673</v>
+        <v>3.880808574301491</v>
       </c>
       <c r="N24" t="n">
-        <v>30.47085145230751</v>
+        <v>30.21147095696919</v>
       </c>
       <c r="O24" t="n">
-        <v>5.520040892267693</v>
+        <v>5.49649624369645</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0870248490329</v>
+        <v>340.0721464416328</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32887,7 +33160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y335"/>
+  <dimension ref="A1:Y338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74508,7 +74781,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>-38.57776319874085,174.62997489157246</t>
+          <t>-38.57776265023625,174.62987389046586</t>
         </is>
       </c>
       <c r="M333" t="inlineStr"/>
@@ -74631,7 +74904,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>-38.57776309153999,174.6299551504472</t>
+          <t>-38.57776232483209,174.6298139784451</t>
         </is>
       </c>
       <c r="M334" t="inlineStr"/>
@@ -74744,7 +75017,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>-38.5791644107992,174.63000199319</t>
+          <t>-38.57916532219422,174.62984681637494</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -74754,7 +75027,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>-38.57776309153999,174.6299551504472</t>
+          <t>-38.57776232483209,174.6298139784451</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -74774,7 +75047,7 @@
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>-38.57495889656735,174.63003321184613</t>
+          <t>-38.574956613962826,174.62992743177603</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
@@ -74818,6 +75091,387 @@
         </is>
       </c>
       <c r="Y335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-38.58478340852851,174.62957059463122</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-38.584088417647585,174.6297458829365</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-38.583397291580276,174.63000079254613</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-38.58270624980941,174.63053387276614</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-38.58197822820121,174.63016894573022</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-38.58127073807359,174.63005713101109</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-38.580568159801494,174.63011978455907</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-38.579866365624724,174.6300478037029</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-38.57916565852249,174.62978954327244</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-38.578460455884255,174.63029545742464</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>-38.57776225376273,174.6298008942106</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-38.577082841571915,174.63092906435486</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-38.57636966474847,174.63029962945404</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-38.575667876027936,174.63033289231413</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>-38.574956742702284,174.6299333976801</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>-38.57426904848629,174.63032981679504</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>-38.57357390734749,174.63034297033</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>-38.572853938098966,174.63003380920847</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>-38.57215189041912,174.6300673964193</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>-38.57145962677533,174.6304025976085</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>-38.57075374995942,174.63037826902297</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>-38.57005158214094,174.63036905281533</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>-38.569349306690626,174.63036261327017</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-38.58478340852851,174.62957059463122</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-38.584088417647585,174.6297458829365</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-38.583397291580276,174.63000079254613</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-38.58270624980941,174.63053387276614</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-38.58197822820121,174.63016894573022</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-38.581270252547434,174.63013977195965</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-38.58056741660828,174.63024626988502</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-38.579866365624724,174.6300478037029</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-38.57916565852249,174.62978954327244</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-38.578460455884255,174.63029545742464</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>-38.57776225376273,174.6298008942106</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>-38.577082841571915,174.63092906435486</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-38.57637241972425,174.63042732525446</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-38.57567012605812,174.63043718193776</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>-38.574956742702284,174.6299333976801</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>-38.57426904848629,174.63032981679504</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>-38.57357390734749,174.63034297033</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>-38.57285540288233,174.63005990991203</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>-38.572154017188005,174.63011138390712</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>-38.57146168375563,174.6304734750026</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>-38.57075374995942,174.63037826902297</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>-38.570052352742856,174.63040702716125</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>-38.56934981566148,174.63038463828877</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-38.584784851470076,174.62960026781124</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-38.58409049008435,174.6297885019211</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-38.58339444484626,174.62994224928647</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-38.58270624980941,174.63053387276614</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-38.58197842799805,174.63020096929685</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-38.581270252547434,174.63013977195965</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-38.58056741660828,174.63024626988502</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-38.579865313656875,174.63022685560023</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-38.5791642543853,174.63002862116306</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-38.57846033245769,174.6303164611787</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-38.57776377270734,174.63008059841073</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-38.577082841571915,174.63092906435486</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-38.57637241972425,174.63042732525446</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-38.575670809217186,174.6304688474347</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-38.57496164695377,174.63016067568768</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>-38.574270669138954,174.63037579370194</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>-38.57357293884201,174.63032453358426</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>-38.57285454842608,174.63004468450148</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>-38.572154017188005,174.63011138390712</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>-38.57146168375563,174.6304734750026</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>-38.570755326105854,174.6304684524064</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>-38.570052352742856,174.63040702716125</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>-38.56934936766131,174.63036525168383</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y338"/>
+  <dimension ref="A1:Y339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27490,10 +27490,10 @@
         <v>310.83</v>
       </c>
       <c r="G338" t="n">
-        <v>316.5</v>
+        <v>316.44</v>
       </c>
       <c r="H338" t="n">
-        <v>307.55</v>
+        <v>309.34</v>
       </c>
       <c r="I338" t="n">
         <v>309.57</v>
@@ -27511,7 +27511,7 @@
         <v>251.91</v>
       </c>
       <c r="N338" t="n">
-        <v>298.7</v>
+        <v>296.75</v>
       </c>
       <c r="O338" t="n">
         <v>298.15</v>
@@ -27529,7 +27529,7 @@
         <v>353.52</v>
       </c>
       <c r="T338" t="n">
-        <v>354.22</v>
+        <v>355.83</v>
       </c>
       <c r="U338" t="n">
         <v>327.63</v>
@@ -27538,7 +27538,7 @@
         <v>330.75</v>
       </c>
       <c r="W338" t="n">
-        <v>338.76</v>
+        <v>341.03</v>
       </c>
       <c r="X338" t="n">
         <v>345.62</v>
@@ -27546,6 +27546,87 @@
       <c r="Y338" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>346.49</v>
+      </c>
+      <c r="C339" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="D339" t="n">
+        <v>324.77</v>
+      </c>
+      <c r="E339" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="F339" t="n">
+        <v>312.62</v>
+      </c>
+      <c r="G339" t="n">
+        <v>317.52</v>
+      </c>
+      <c r="H339" t="n">
+        <v>311.66</v>
+      </c>
+      <c r="I339" t="n">
+        <v>297.34</v>
+      </c>
+      <c r="J339" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="K339" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="L339" t="n">
+        <v>303.62</v>
+      </c>
+      <c r="M339" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="N339" t="n">
+        <v>290.61</v>
+      </c>
+      <c r="O339" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="P339" t="n">
+        <v>328.08</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>312.36</v>
+      </c>
+      <c r="R339" t="n">
+        <v>322.57</v>
+      </c>
+      <c r="S339" t="n">
+        <v>354</v>
+      </c>
+      <c r="T339" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="U339" t="n">
+        <v>325.04</v>
+      </c>
+      <c r="V339" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="W339" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="X339" t="n">
+        <v>345.16</v>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B365"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31213,6 +31294,16 @@
       </c>
       <c r="B365" t="n">
         <v>1.02</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -31381,28 +31472,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7473972774902912</v>
+        <v>0.7421243391492015</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1200591053834797</v>
+        <v>0.1190189718236456</v>
       </c>
       <c r="M2" t="n">
-        <v>11.95707642141918</v>
+        <v>11.94770511012716</v>
       </c>
       <c r="N2" t="n">
-        <v>226.705054718708</v>
+        <v>226.2972976908291</v>
       </c>
       <c r="O2" t="n">
-        <v>15.05672788884451</v>
+        <v>15.04318110277308</v>
       </c>
       <c r="P2" t="n">
-        <v>336.2421013050798</v>
+        <v>336.3003784374408</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31459,28 +31550,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1593765104396153</v>
+        <v>-0.1616833193274491</v>
       </c>
       <c r="J3" t="n">
+        <v>338</v>
+      </c>
+      <c r="K3" t="n">
         <v>337</v>
       </c>
-      <c r="K3" t="n">
-        <v>336</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.004930717138065144</v>
+        <v>0.005100825302639223</v>
       </c>
       <c r="M3" t="n">
-        <v>11.91253220033434</v>
+        <v>11.89353318427336</v>
       </c>
       <c r="N3" t="n">
-        <v>286.6653134122733</v>
+        <v>285.8684130224814</v>
       </c>
       <c r="O3" t="n">
-        <v>16.93119350229845</v>
+        <v>16.90764362714336</v>
       </c>
       <c r="P3" t="n">
-        <v>338.1570262460433</v>
+        <v>338.1822073678537</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31537,28 +31628,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1424150463602835</v>
+        <v>-0.1463588062045066</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003433609603211929</v>
+        <v>0.003644024045629135</v>
       </c>
       <c r="M4" t="n">
-        <v>13.24842243440673</v>
+        <v>13.23596085047962</v>
       </c>
       <c r="N4" t="n">
-        <v>327.1448336824633</v>
+        <v>326.3214797569753</v>
       </c>
       <c r="O4" t="n">
-        <v>18.08714553716156</v>
+        <v>18.06437045005929</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8099368416441</v>
+        <v>335.8532650176846</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31615,28 +31706,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6718967081893222</v>
+        <v>0.6350546128732268</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0429837721503199</v>
+        <v>0.03793106945554658</v>
       </c>
       <c r="M5" t="n">
-        <v>19.04931613534733</v>
+        <v>19.22579346226072</v>
       </c>
       <c r="N5" t="n">
-        <v>560.9259707192462</v>
+        <v>572.3209089253074</v>
       </c>
       <c r="O5" t="n">
-        <v>23.68387575375378</v>
+        <v>23.92322948360667</v>
       </c>
       <c r="P5" t="n">
-        <v>325.9060026676552</v>
+        <v>326.3110318463295</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31693,28 +31784,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.331390695042441</v>
+        <v>0.3287261393768076</v>
       </c>
       <c r="J6" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K6" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008576852807590019</v>
+        <v>0.008486165614428165</v>
       </c>
       <c r="M6" t="n">
-        <v>19.16390877345485</v>
+        <v>19.12602863962027</v>
       </c>
       <c r="N6" t="n">
-        <v>707.1377160987984</v>
+        <v>705.0920866589142</v>
       </c>
       <c r="O6" t="n">
-        <v>26.59206114799675</v>
+        <v>26.55357013018992</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7090186116847</v>
+        <v>308.7382539211951</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31771,28 +31862,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06199791907083704</v>
+        <v>0.05797772287307853</v>
       </c>
       <c r="J7" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004792342775269409</v>
+        <v>0.0004213247838631418</v>
       </c>
       <c r="M7" t="n">
-        <v>15.44827038989944</v>
+        <v>15.43352014936679</v>
       </c>
       <c r="N7" t="n">
-        <v>446.6562836255103</v>
+        <v>445.4720050160214</v>
       </c>
       <c r="O7" t="n">
-        <v>21.13424433533194</v>
+        <v>21.10620773649358</v>
       </c>
       <c r="P7" t="n">
-        <v>323.1457595832088</v>
+        <v>323.1897902223893</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31849,28 +31940,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08952574150058318</v>
+        <v>0.07922934875079451</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K8" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003672542402481049</v>
+        <v>0.002870290371540074</v>
       </c>
       <c r="M8" t="n">
-        <v>8.944072998840825</v>
+        <v>8.983096801377727</v>
       </c>
       <c r="N8" t="n">
-        <v>121.8172539392017</v>
+        <v>122.4847126817422</v>
       </c>
       <c r="O8" t="n">
-        <v>11.03708539149724</v>
+        <v>11.06728117839888</v>
       </c>
       <c r="P8" t="n">
-        <v>330.1454116794267</v>
+        <v>330.2577816804586</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31927,28 +32018,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05510431762074602</v>
+        <v>0.03514505131644052</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005817682783368916</v>
+        <v>0.00023477987407583</v>
       </c>
       <c r="M9" t="n">
-        <v>12.39755159596115</v>
+        <v>12.49926401151848</v>
       </c>
       <c r="N9" t="n">
-        <v>293.0740460936482</v>
+        <v>296.2554857041497</v>
       </c>
       <c r="O9" t="n">
-        <v>17.11940554147977</v>
+        <v>17.21207383507722</v>
       </c>
       <c r="P9" t="n">
-        <v>332.8486581372898</v>
+        <v>333.0664243854844</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32005,28 +32096,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1261708167904721</v>
+        <v>0.1286133977507622</v>
       </c>
       <c r="J10" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K10" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00383051170348514</v>
+        <v>0.004000580406208876</v>
       </c>
       <c r="M10" t="n">
-        <v>12.82243644793013</v>
+        <v>12.794844939773</v>
       </c>
       <c r="N10" t="n">
-        <v>230.1753284285758</v>
+        <v>229.5462081863078</v>
       </c>
       <c r="O10" t="n">
-        <v>15.17153019403698</v>
+        <v>15.15078242818858</v>
       </c>
       <c r="P10" t="n">
-        <v>319.3122680019385</v>
+        <v>319.2854301628687</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32083,28 +32174,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05460771129485705</v>
+        <v>0.04386408535223314</v>
       </c>
       <c r="J11" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K11" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006095749731656053</v>
+        <v>0.0003938856825270731</v>
       </c>
       <c r="M11" t="n">
-        <v>13.6414192305115</v>
+        <v>13.66409978108592</v>
       </c>
       <c r="N11" t="n">
-        <v>273.0731183988015</v>
+        <v>273.4230727410487</v>
       </c>
       <c r="O11" t="n">
-        <v>16.52492415712706</v>
+        <v>16.53550944909314</v>
       </c>
       <c r="P11" t="n">
-        <v>314.6696801125975</v>
+        <v>314.7873574852182</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32161,28 +32252,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4010018831178611</v>
+        <v>0.3870070163711268</v>
       </c>
       <c r="J12" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K12" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03970880575624136</v>
+        <v>0.03697351159742668</v>
       </c>
       <c r="M12" t="n">
-        <v>12.14717410899306</v>
+        <v>12.21087037927541</v>
       </c>
       <c r="N12" t="n">
-        <v>218.7427302191126</v>
+        <v>220.0124296886537</v>
       </c>
       <c r="O12" t="n">
-        <v>14.78995369225721</v>
+        <v>14.83281597299224</v>
       </c>
       <c r="P12" t="n">
-        <v>318.2319532068291</v>
+        <v>318.3842165857093</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32239,28 +32330,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.764608308000791</v>
+        <v>-0.7936410472936366</v>
       </c>
       <c r="J13" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K13" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02890045613715786</v>
+        <v>0.0310431373545087</v>
       </c>
       <c r="M13" t="n">
-        <v>28.39649223896004</v>
+        <v>28.48979803741048</v>
       </c>
       <c r="N13" t="n">
-        <v>1115.558927942701</v>
+        <v>1119.672147720573</v>
       </c>
       <c r="O13" t="n">
-        <v>33.39998395123419</v>
+        <v>33.46150247255154</v>
       </c>
       <c r="P13" t="n">
-        <v>321.1716604191314</v>
+        <v>321.484575800033</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32317,28 +32408,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2192048640495821</v>
+        <v>-0.2246543581987467</v>
       </c>
       <c r="J14" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K14" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005818250542006465</v>
+        <v>0.006140221326868645</v>
       </c>
       <c r="M14" t="n">
-        <v>18.41416133365595</v>
+        <v>18.38954477651481</v>
       </c>
       <c r="N14" t="n">
-        <v>461.6623756858295</v>
+        <v>460.4926069870196</v>
       </c>
       <c r="O14" t="n">
-        <v>21.48632997246923</v>
+        <v>21.45909147627223</v>
       </c>
       <c r="P14" t="n">
-        <v>304.60299976056</v>
+        <v>304.6623442353224</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32395,28 +32486,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1420178510285227</v>
+        <v>0.1368607349115782</v>
       </c>
       <c r="J15" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K15" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003189799044963082</v>
+        <v>0.002977075460298795</v>
       </c>
       <c r="M15" t="n">
-        <v>16.1088120001134</v>
+        <v>16.0905716563026</v>
       </c>
       <c r="N15" t="n">
-        <v>354.9063910760921</v>
+        <v>354.1152863304864</v>
       </c>
       <c r="O15" t="n">
-        <v>18.83895939472486</v>
+        <v>18.81795117249714</v>
       </c>
       <c r="P15" t="n">
-        <v>303.9308656455211</v>
+        <v>303.9870378469403</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32473,28 +32564,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3392858421136531</v>
+        <v>0.3421865464809354</v>
       </c>
       <c r="J16" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K16" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01063795450599869</v>
+        <v>0.01087643122824822</v>
       </c>
       <c r="M16" t="n">
-        <v>20.03230106054498</v>
+        <v>19.98660963192259</v>
       </c>
       <c r="N16" t="n">
-        <v>594.1794272242802</v>
+        <v>592.4741929242485</v>
       </c>
       <c r="O16" t="n">
-        <v>24.37579593006719</v>
+        <v>24.34079277517987</v>
       </c>
       <c r="P16" t="n">
-        <v>313.7378496375323</v>
+        <v>313.7059006179931</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32551,28 +32642,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6806978549314379</v>
+        <v>-0.6803402841890095</v>
       </c>
       <c r="J17" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K17" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03795346871191974</v>
+        <v>0.03812793779690904</v>
       </c>
       <c r="M17" t="n">
-        <v>21.23392697074636</v>
+        <v>21.16847988979152</v>
       </c>
       <c r="N17" t="n">
-        <v>651.997601484853</v>
+        <v>649.9223950865791</v>
       </c>
       <c r="O17" t="n">
-        <v>25.53424370301288</v>
+        <v>25.49357556496497</v>
       </c>
       <c r="P17" t="n">
-        <v>329.8548406345076</v>
+        <v>329.8508997075838</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32629,28 +32720,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1084066254904051</v>
+        <v>-0.109059252128788</v>
       </c>
       <c r="J18" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K18" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005614922228217689</v>
+        <v>0.005713595102393998</v>
       </c>
       <c r="M18" t="n">
-        <v>8.414329548575418</v>
+        <v>8.393837398343177</v>
       </c>
       <c r="N18" t="n">
-        <v>115.4004061582148</v>
+        <v>115.0612048795332</v>
       </c>
       <c r="O18" t="n">
-        <v>10.74245810595577</v>
+        <v>10.72665860739183</v>
       </c>
       <c r="P18" t="n">
-        <v>326.6515825948189</v>
+        <v>326.6587502576153</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32707,28 +32798,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2256609059137669</v>
+        <v>0.2268782820319594</v>
       </c>
       <c r="J19" t="n">
+        <v>338</v>
+      </c>
+      <c r="K19" t="n">
         <v>337</v>
       </c>
-      <c r="K19" t="n">
-        <v>336</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.03902036322193769</v>
+        <v>0.03962792651622671</v>
       </c>
       <c r="M19" t="n">
-        <v>6.300828630766577</v>
+        <v>6.287194126208428</v>
       </c>
       <c r="N19" t="n">
-        <v>70.13241915607107</v>
+        <v>69.93927730458248</v>
       </c>
       <c r="O19" t="n">
-        <v>8.374510084540532</v>
+        <v>8.362970602876855</v>
       </c>
       <c r="P19" t="n">
-        <v>345.7439041213494</v>
+        <v>345.730615245759</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32785,28 +32876,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09428253784568381</v>
+        <v>0.09935592764223088</v>
       </c>
       <c r="J20" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K20" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006055877555797839</v>
+        <v>0.006736518700251826</v>
       </c>
       <c r="M20" t="n">
-        <v>7.123902033130928</v>
+        <v>7.134996626014876</v>
       </c>
       <c r="N20" t="n">
-        <v>81.73820268591555</v>
+        <v>81.75238041502287</v>
       </c>
       <c r="O20" t="n">
-        <v>9.040918243514623</v>
+        <v>9.041702296305871</v>
       </c>
       <c r="P20" t="n">
-        <v>344.2930925465403</v>
+        <v>344.2377398943026</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32863,28 +32954,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2906442665746281</v>
+        <v>0.2883815373609614</v>
       </c>
       <c r="J21" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K21" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02152440481241513</v>
+        <v>0.02130776588047101</v>
       </c>
       <c r="M21" t="n">
-        <v>11.81102382334768</v>
+        <v>11.78768638831433</v>
       </c>
       <c r="N21" t="n">
-        <v>213.379145209852</v>
+        <v>212.791666578347</v>
       </c>
       <c r="O21" t="n">
-        <v>14.60750304500574</v>
+        <v>14.58738038779914</v>
       </c>
       <c r="P21" t="n">
-        <v>321.4657335354685</v>
+        <v>321.490595125927</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32941,28 +33032,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4272414007126071</v>
+        <v>0.4368201283391756</v>
       </c>
       <c r="J22" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K22" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02813397901038939</v>
+        <v>0.02945478978351079</v>
       </c>
       <c r="M22" t="n">
-        <v>15.14082006239156</v>
+        <v>15.14972733425141</v>
       </c>
       <c r="N22" t="n">
-        <v>353.9213924724298</v>
+        <v>353.7992453906514</v>
       </c>
       <c r="O22" t="n">
-        <v>18.81279863477069</v>
+        <v>18.80955197208725</v>
       </c>
       <c r="P22" t="n">
-        <v>301.6193104263991</v>
+        <v>301.5149292255065</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33019,28 +33110,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5010564544065578</v>
+        <v>0.5050188003942218</v>
       </c>
       <c r="J23" t="n">
+        <v>338</v>
+      </c>
+      <c r="K23" t="n">
         <v>337</v>
       </c>
-      <c r="K23" t="n">
-        <v>336</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1243114794108495</v>
+        <v>0.1265094319787142</v>
       </c>
       <c r="M23" t="n">
-        <v>7.717503263007018</v>
+        <v>7.709560392216878</v>
       </c>
       <c r="N23" t="n">
-        <v>98.8997130027869</v>
+        <v>98.72963298941872</v>
       </c>
       <c r="O23" t="n">
-        <v>9.944833482908948</v>
+        <v>9.936278628813643</v>
       </c>
       <c r="P23" t="n">
-        <v>322.9896326722451</v>
+        <v>322.946394149888</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33097,28 +33188,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1597090213591316</v>
+        <v>0.1601599328942699</v>
       </c>
       <c r="J24" t="n">
+        <v>338</v>
+      </c>
+      <c r="K24" t="n">
         <v>337</v>
       </c>
-      <c r="K24" t="n">
-        <v>336</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04498002109679922</v>
+        <v>0.04545974767534322</v>
       </c>
       <c r="M24" t="n">
-        <v>3.880808574301491</v>
+        <v>3.871500264741989</v>
       </c>
       <c r="N24" t="n">
-        <v>30.21147095696919</v>
+        <v>30.123869415704</v>
       </c>
       <c r="O24" t="n">
-        <v>5.49649624369645</v>
+        <v>5.488521605651561</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0721464416328</v>
+        <v>340.0672164280061</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -33160,7 +33251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y338"/>
+  <dimension ref="A1:Y339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75383,12 +75474,12 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>-38.581270252547434,174.63013977195965</t>
+          <t>-38.58127024850115,174.6301404606342</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>-38.58056741660828,174.63024626988502</t>
+          <t>-38.580567537335895,174.6302257246284</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -75418,7 +75509,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>-38.57637241972425,174.63042732525446</t>
+          <t>-38.57637290238758,174.63044969783454</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -75448,7 +75539,7 @@
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>-38.572154017188005,174.63011138390712</t>
+          <t>-38.572153125497856,174.6300929412362</t>
         </is>
       </c>
       <c r="U338" t="inlineStr">
@@ -75463,7 +75554,7 @@
       </c>
       <c r="W338" t="inlineStr">
         <is>
-          <t>-38.570052352742856,174.63040702716125</t>
+          <t>-38.57005182426492,174.63038098433182</t>
         </is>
       </c>
       <c r="X338" t="inlineStr">
@@ -75474,6 +75565,133 @@
       <c r="Y338" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-38.5847829516883,174.62956120003386</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-38.584092038830676,174.62982035159362</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-38.58339444484626,174.62994224928647</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-38.58270624980941,174.63053387276614</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-38.58197829981398,174.6301804237111</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-38.58127032133386,174.63012806449214</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-38.580567693804305,174.63019909613908</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-38.57986448874949,174.63036722768618</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-38.5791642543853,174.63002862116306</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-38.57845991898497,174.6303868180146</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-38.57776499822028,174.63030635882933</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-38.577082841571915,174.63092906435486</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-38.576374422130286,174.63052014277994</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-38.575670809217186,174.6304688474347</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-38.57496164695377,174.63016067568768</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>-38.574270669138954,174.63037579370194</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>-38.57357293884201,174.63032453358426</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>-38.5728542400504,174.63003918961658</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>-38.572153806727236,174.63010703097856</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>-38.57146254581063,174.6305031792834</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>-38.570755326105854,174.6304684524064</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>-38.57005173812481,174.6303767394654</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>-38.5693494896025,174.6303705285112</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
